--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_152_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_152_R16.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>L. BROWN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7942</v>
+        <v>4.2795</v>
       </c>
       <c r="E2" t="n">
-        <v>4.202</v>
+        <v>3.862</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4078</v>
+        <v>0.4174</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3159</v>
+        <v>5.4029</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.2701</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4132</v>
+        <v>5.1327</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0514</v>
+        <v>4.1056</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5279</v>
+        <v>0.0203</v>
       </c>
       <c r="L2" t="n">
-        <v>4.5235</v>
+        <v>4.0854</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2645</v>
+        <v>1.2972</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3748</v>
+        <v>0.2499</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1103</v>
+        <v>1.0474</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8105</v>
+        <v>-0.747</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1202</v>
+        <v>-0.2436</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3097</v>
+        <v>-0.5034</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. BROWN</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6568</v>
+        <v>3.8291</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5082</v>
+        <v>4.6738</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1486</v>
+        <v>-0.8447</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4029</v>
+        <v>5.3159</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2701</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1327</v>
+        <v>4.4132</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1056</v>
+        <v>5.0514</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0203</v>
+        <v>0.5279</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0854</v>
+        <v>4.5235</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2972</v>
+        <v>0.2645</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2499</v>
+        <v>0.3748</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0474</v>
+        <v>-0.1103</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3697</v>
+        <v>-0.7756</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5975</v>
+        <v>-0.6484</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7723</v>
+        <v>-0.1272</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4538</v>
+        <v>2.6548</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7466</v>
+        <v>1.5107</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7071</v>
+        <v>1.144</v>
       </c>
       <c r="G4" t="n">
         <v>5.1858</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2681</v>
+        <v>-2.0671</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4086</v>
+        <v>-0.6445</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.8595</v>
+        <v>-1.4227</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.021</v>
+        <v>1.2741</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1449</v>
+        <v>-1.7911</v>
       </c>
       <c r="F5" t="n">
-        <v>3.166</v>
+        <v>3.0652</v>
       </c>
       <c r="G5" t="n">
         <v>2.5917</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8026</v>
+        <v>-0.5496</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8215</v>
+        <v>-0.4676</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0189</v>
+        <v>-0.0819</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5361</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0118</v>
+        <v>0.4385</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3773</v>
+        <v>-0.3304</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6345</v>
+        <v>0.7689</v>
       </c>
       <c r="G6" t="n">
         <v>0.5484</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1423</v>
+        <v>-0.7156</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6018</v>
+        <v>-0.1059</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7442</v>
+        <v>-0.6097</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0151</v>
+        <v>-0.655</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9022</v>
+        <v>3.4304</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9173</v>
+        <v>-4.0853</v>
       </c>
       <c r="G7" t="n">
         <v>1.2649</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9063</v>
+        <v>-1.5461</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>-0.6563</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7218</v>
+        <v>-0.8898</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3696</v>
+        <v>-1.4533</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5473</v>
+        <v>-2.4294</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1777</v>
+        <v>0.9761</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3297</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6482</v>
+        <v>-1.7319</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2696</v>
+        <v>-1.1516</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3787</v>
+        <v>-0.5803</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9882</v>
+        <v>-2.0554</v>
       </c>
       <c r="E9" t="n">
         <v>-1.7522</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.236</v>
+        <v>-0.3032</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9352</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.303</v>
+        <v>-1.3702</v>
       </c>
       <c r="T9" t="n">
         <v>-0.8215</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4815</v>
+        <v>-0.5487</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5411</v>
+        <v>-2.2887</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3533</v>
+        <v>-1.2353</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1878</v>
+        <v>-1.0534</v>
       </c>
       <c r="G10" t="n">
         <v>2.0037</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.171</v>
+        <v>-1.9186</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1949</v>
+        <v>-1.0769</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9761</v>
+        <v>-0.8417</v>
       </c>
       <c r="V10" t="n">
         <v>-1.214</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.0236</v>
+        <v>6.023599999999997</v>
       </c>
       <c r="E11" t="n">
-        <v>5.938600000000001</v>
+        <v>5.938499999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08500000000000019</v>
+        <v>0.08499999999999996</v>
       </c>
       <c r="G11" t="n">
         <v>20.0484</v>
@@ -1315,10 +1315,10 @@
         <v>-11.4217</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.8165</v>
+        <v>-5.8163</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.6055</v>
+        <v>-5.6054</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2836</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.5404</v>
+        <v>8.6342</v>
       </c>
       <c r="E12" t="n">
-        <v>6.9399</v>
+        <v>7.5296</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6005</v>
+        <v>1.1046</v>
       </c>
       <c r="G12" t="n">
         <v>7.2754</v>
@@ -1390,13 +1390,13 @@
         <v>2.3195</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.1628</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1098</v>
+        <v>0.4799</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1788</v>
+        <v>0.6829</v>
       </c>
       <c r="V12" t="n">
         <v>1.3558</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4339</v>
+        <v>1.2871</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1667</v>
+        <v>0.0305</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7328</v>
+        <v>1.2566</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6575</v>
+        <v>0.9384</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3372</v>
+        <v>-0.0755</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.9946</v>
+        <v>1.0138</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0105</v>
+        <v>1.9212</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5832</v>
+        <v>0.168</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5727</v>
+        <v>1.7532</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6679</v>
+        <v>-0.9829</v>
       </c>
       <c r="N13" t="n">
-        <v>0.754</v>
+        <v>-0.2435</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.422</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R13" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3955</v>
+        <v>1.1863</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6201</v>
+        <v>0.4288</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7754</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7144</v>
+        <v>0.3939</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4413</v>
+        <v>0.7621</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1557</v>
+        <v>-0.3682</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9384</v>
+        <v>-3.1135</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0755</v>
+        <v>-1.1595</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0138</v>
+        <v>-1.9539</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9212</v>
+        <v>0.1603</v>
       </c>
       <c r="K14" t="n">
-        <v>0.168</v>
+        <v>-0.0973</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7532</v>
+        <v>0.2576</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9829</v>
+        <v>-3.2738</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2435</v>
+        <v>-1.0622</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-2.2116</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6137</v>
+        <v>1.7034</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0431</v>
+        <v>0.6018</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6568000000000001</v>
+        <v>1.1015</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6291</v>
+        <v>0.3564</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7621</v>
+        <v>0.9605</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.133</v>
+        <v>-0.6041</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1135</v>
+        <v>-2.5026</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1595</v>
+        <v>0.1741</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9539</v>
+        <v>-2.6767</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1603</v>
+        <v>-1.3916</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0973</v>
+        <v>-0.7156</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2576</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.2738</v>
+        <v>-1.1111</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0622</v>
+        <v>0.8897</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2116</v>
+        <v>-2.0008</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0876</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9386</v>
+        <v>0.3383</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6018</v>
+        <v>0.2952</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3368</v>
+        <v>0.0431</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2836</v>
+        <v>3.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5187</v>
+        <v>0.1206</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4887</v>
+        <v>1.2231</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0074</v>
+        <v>-1.1025</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5026</v>
+        <v>-0.6575</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1741</v>
+        <v>2.3372</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6767</v>
+        <v>-2.9946</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3916</v>
+        <v>0.0105</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7156</v>
+        <v>1.5832</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.5727</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1111</v>
+        <v>-0.6679</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8897</v>
+        <v>0.754</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0008</v>
+        <v>-1.422</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5368000000000001</v>
+        <v>1.0822</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1766</v>
+        <v>0.6765</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3602</v>
+        <v>0.4057</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2166</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>3.2166</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4992</v>
+        <v>-1.1854</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9768</v>
+        <v>-0.2991</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5224</v>
+        <v>-0.8863</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3423</v>
+        <v>-0.9509</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0228</v>
+        <v>0.2904</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3652</v>
+        <v>-1.2413</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7527</v>
+        <v>-0.39</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0336</v>
+        <v>0.3228</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7863</v>
+        <v>-0.7127</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5896</v>
+        <v>-0.5609</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0108</v>
+        <v>-0.0323</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5788</v>
+        <v>-0.5286</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1568</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.224</v>
+        <v>-0.051</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0672</v>
+        <v>0.051</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5228</v>
+        <v>-1.2804</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7709</v>
+        <v>-0.8588</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7519</v>
+        <v>-0.4216</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9509</v>
+        <v>-1.3423</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2904</v>
+        <v>0.0228</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2413</v>
+        <v>-1.3652</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.39</v>
+        <v>-0.7527</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3228</v>
+        <v>0.0336</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7127</v>
+        <v>-0.7863</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5609</v>
+        <v>-0.5896</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0323</v>
+        <v>-0.0108</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5286</v>
+        <v>-0.5788</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3374</v>
+        <v>0.0619</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.1061</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1854</v>
+        <v>0.168</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7459</v>
+        <v>-1.3584</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.045</v>
+        <v>-1.6912</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2992</v>
+        <v>0.3328</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8509</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.127</v>
+        <v>0.2605</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3958</v>
+        <v>0.4294</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7858</v>
+        <v>-2.2143</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2853</v>
+        <v>-1.2549</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5005</v>
+        <v>-0.9593</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.2206</v>
+        <v>-4.6903</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.4276</v>
+        <v>-0.0961</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.793</v>
+        <v>-4.5942</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6402</v>
+        <v>-2.4779</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.5334</v>
+        <v>0.3263</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8932</v>
+        <v>-2.8042</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5804</v>
+        <v>-2.2123</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8942</v>
+        <v>-0.4223</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6862</v>
+        <v>-1.79</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8291</v>
+        <v>1.9246</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3882</v>
+        <v>1.223</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4409</v>
+        <v>0.7016</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8097</v>
+        <v>-2.6609</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7831</v>
+        <v>-0.7571</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0265</v>
+        <v>-1.9038</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.6903</v>
+        <v>-4.2206</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0961</v>
+        <v>-3.4276</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.5942</v>
+        <v>-0.793</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.4779</v>
+        <v>-1.6402</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3263</v>
+        <v>-2.5334</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.8042</v>
+        <v>0.8932</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2123</v>
+        <v>-2.5804</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4223</v>
+        <v>-0.8942</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.79</v>
+        <v>-1.6862</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3292</v>
+        <v>1.954</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6948</v>
+        <v>0.9164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6344</v>
+        <v>1.0376</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5346</v>
+        <v>-3.3774</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5741</v>
+        <v>-2.5177</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9606</v>
+        <v>-0.8597</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4327</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7383</v>
+        <v>0.8955</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7695</v>
+        <v>0.8259</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0312</v>
+        <v>0.0696</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9246</v>
+        <v>-4.7388</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5657</v>
+        <v>-3.2119</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3589</v>
+        <v>-1.527</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5009</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6664</v>
+        <v>0.8522</v>
       </c>
       <c r="T23" t="n">
-        <v>0.13</v>
+        <v>0.4839</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0235</v>
+        <v>-6.023400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.08480000000000043</v>
+        <v>-0.08489999999999975</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.9386</v>
+        <v>-5.938499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-20.0484</v>
@@ -2299,10 +2299,10 @@
         <v>-17.0647</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.539199999999999</v>
+        <v>-4.539200000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.015299999999999</v>
+        <v>-3.0153</v>
       </c>
       <c r="L24" t="n">
         <v>-1.5237</v>
@@ -2311,7 +2311,7 @@
         <v>-15.5092</v>
       </c>
       <c r="N24" t="n">
-        <v>0.03170000000000017</v>
+        <v>0.03169999999999995</v>
       </c>
       <c r="O24" t="n">
         <v>-15.5411</v>
@@ -2326,16 +2326,16 @@
         <v>12.7576</v>
       </c>
       <c r="S24" t="n">
-        <v>11.4218</v>
+        <v>11.4217</v>
       </c>
       <c r="T24" t="n">
-        <v>5.6053</v>
+        <v>5.6054</v>
       </c>
       <c r="U24" t="n">
-        <v>5.8165</v>
+        <v>5.816400000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2836</v>
+        <v>0.2836000000000004</v>
       </c>
       <c r="W24" t="n">
         <v>9.2866</v>
